--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,1624 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128347619</v>
+      </c>
+      <c r="B3" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>703525</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6359615</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128347624</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102606</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>703584</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6359603</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1,6 m hög. Inga frukter.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128347623</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102606</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>703583</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6359604</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 m hög. Inga frukter.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128347617</v>
+      </c>
+      <c r="B6" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>703486</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6359605</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128347622</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102606</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>703571</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6359615</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,3 m hög. 3 stammar 1 + 1,5 + 4 cm i daimeter. Medfrukter.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Jord- och stenhög i gles kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128347626</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102606</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>703592</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6359590</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0,5 m hög; Under staket mot körväg.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128347614</v>
+      </c>
+      <c r="B9" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>703479</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6359603</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128347627</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102606</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>703491</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6359527</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1,8 m hög; spenslig 1 stam 0,5 cm i diameter. Inga frukter.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128347610</v>
+      </c>
+      <c r="B11" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>703443</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6359606</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128347625</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102606</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>703585</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6359601</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128347345</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5477</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105894</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Smedbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ergates faber</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1761)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>703485</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6359521</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128347621</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102606</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>703557</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6359619</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>6,5 m hög; Frukter ses. Stam 9 cm i diameter samt delstam 3 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128347632</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102606</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>703485</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6359521</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1,8 m hög; 1 stm 2 cm i diameter. Inga frukter.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128347607</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106769</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>703439</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6359632</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128347619</v>
       </c>
       <c r="B3" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128347624</v>
       </c>
       <c r="B4" t="n">
-        <v>102606</v>
+        <v>102611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>128347623</v>
       </c>
       <c r="B5" t="n">
-        <v>102606</v>
+        <v>102611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>128347617</v>
       </c>
       <c r="B6" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>128347622</v>
       </c>
       <c r="B7" t="n">
-        <v>102606</v>
+        <v>102611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128347626</v>
       </c>
       <c r="B8" t="n">
-        <v>102606</v>
+        <v>102611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128347614</v>
       </c>
       <c r="B9" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128347627</v>
       </c>
       <c r="B10" t="n">
-        <v>102606</v>
+        <v>102611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>128347610</v>
       </c>
       <c r="B11" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,32 +1825,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128347625</v>
+        <v>128347345</v>
       </c>
       <c r="B12" t="n">
-        <v>102606</v>
+        <v>5477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>105894</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1860,12 +1860,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1874,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703585</v>
+        <v>703485</v>
       </c>
       <c r="R12" t="n">
-        <v>6359601</v>
+        <v>6359521</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1912,11 +1922,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1928,7 +1933,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1946,32 +1951,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128347345</v>
+        <v>128347625</v>
       </c>
       <c r="B13" t="n">
-        <v>5477</v>
+        <v>102611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105894</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1981,22 +1986,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2005,10 +2000,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703485</v>
+        <v>703585</v>
       </c>
       <c r="R13" t="n">
-        <v>6359521</v>
+        <v>6359601</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2043,6 +2038,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
         <v>128347621</v>
       </c>
       <c r="B14" t="n">
-        <v>102606</v>
+        <v>102611</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128347632</v>
       </c>
       <c r="B15" t="n">
-        <v>102606</v>
+        <v>102611</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128347607</v>
       </c>
       <c r="B16" t="n">
-        <v>106769</v>
+        <v>106774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -798,37 +798,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128347619</v>
+        <v>128347624</v>
       </c>
       <c r="B3" t="n">
-        <v>109305</v>
+        <v>102704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,19 +836,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703525</v>
+        <v>703584</v>
       </c>
       <c r="R3" t="n">
-        <v>6359615</v>
+        <v>6359603</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,6 +885,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1,6 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +901,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,37 +919,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128347624</v>
+        <v>128347619</v>
       </c>
       <c r="B4" t="n">
-        <v>102611</v>
+        <v>109398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -947,24 +957,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703584</v>
+        <v>703525</v>
       </c>
       <c r="R4" t="n">
-        <v>6359603</v>
+        <v>6359615</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,11 +1001,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1,6 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1030,62 +1030,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128347623</v>
+        <v>128347617</v>
       </c>
       <c r="B5" t="n">
-        <v>102611</v>
+        <v>109398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703583</v>
+        <v>703486</v>
       </c>
       <c r="R5" t="n">
-        <v>6359604</v>
+        <v>6359605</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,11 +1103,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1133,7 +1114,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,48 +1132,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128347617</v>
+        <v>128347623</v>
       </c>
       <c r="B6" t="n">
-        <v>109305</v>
+        <v>102704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703486</v>
+        <v>703583</v>
       </c>
       <c r="R6" t="n">
-        <v>6359605</v>
+        <v>6359604</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,6 +1219,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
         <v>128347622</v>
       </c>
       <c r="B7" t="n">
-        <v>102611</v>
+        <v>102704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128347626</v>
       </c>
       <c r="B8" t="n">
-        <v>102611</v>
+        <v>102704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128347614</v>
       </c>
       <c r="B9" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128347627</v>
       </c>
       <c r="B10" t="n">
-        <v>102611</v>
+        <v>102704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>128347610</v>
       </c>
       <c r="B11" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128347625</v>
       </c>
       <c r="B13" t="n">
-        <v>102611</v>
+        <v>102704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>128347621</v>
       </c>
       <c r="B14" t="n">
-        <v>102611</v>
+        <v>102704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128347632</v>
       </c>
       <c r="B15" t="n">
-        <v>102611</v>
+        <v>102704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128347607</v>
       </c>
       <c r="B16" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -798,37 +798,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128347624</v>
+        <v>128347619</v>
       </c>
       <c r="B3" t="n">
-        <v>102704</v>
+        <v>109398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,24 +836,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703584</v>
+        <v>703525</v>
       </c>
       <c r="R3" t="n">
-        <v>6359603</v>
+        <v>6359615</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +880,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1,6 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +891,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,37 +909,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128347619</v>
+        <v>128347624</v>
       </c>
       <c r="B4" t="n">
-        <v>109398</v>
+        <v>102704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,19 +947,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703525</v>
+        <v>703584</v>
       </c>
       <c r="R4" t="n">
-        <v>6359615</v>
+        <v>6359603</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,6 +996,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1,6 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1825,32 +1825,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128347345</v>
+        <v>128347625</v>
       </c>
       <c r="B12" t="n">
-        <v>5477</v>
+        <v>102704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105894</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1860,22 +1860,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1884,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703485</v>
+        <v>703585</v>
       </c>
       <c r="R12" t="n">
-        <v>6359521</v>
+        <v>6359601</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1922,6 +1912,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1933,7 +1928,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1951,32 +1946,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128347625</v>
+        <v>128347345</v>
       </c>
       <c r="B13" t="n">
-        <v>102704</v>
+        <v>5477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>105894</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1986,12 +1981,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2000,10 +2005,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703585</v>
+        <v>703485</v>
       </c>
       <c r="R13" t="n">
-        <v>6359601</v>
+        <v>6359521</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2038,11 +2043,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -798,37 +798,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128347619</v>
+        <v>128347624</v>
       </c>
       <c r="B3" t="n">
-        <v>109398</v>
+        <v>102704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,19 +836,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703525</v>
+        <v>703584</v>
       </c>
       <c r="R3" t="n">
-        <v>6359615</v>
+        <v>6359603</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,6 +885,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1,6 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +901,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,37 +919,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128347624</v>
+        <v>128347619</v>
       </c>
       <c r="B4" t="n">
-        <v>102704</v>
+        <v>109398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -947,24 +957,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703584</v>
+        <v>703525</v>
       </c>
       <c r="R4" t="n">
-        <v>6359603</v>
+        <v>6359615</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,11 +1001,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1,6 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128347624</v>
       </c>
       <c r="B3" t="n">
-        <v>102704</v>
+        <v>102723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>128347619</v>
       </c>
       <c r="B4" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>128347617</v>
       </c>
       <c r="B5" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>128347623</v>
       </c>
       <c r="B6" t="n">
-        <v>102704</v>
+        <v>102723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>128347622</v>
       </c>
       <c r="B7" t="n">
-        <v>102704</v>
+        <v>102723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128347626</v>
       </c>
       <c r="B8" t="n">
-        <v>102704</v>
+        <v>102723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128347614</v>
       </c>
       <c r="B9" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128347627</v>
       </c>
       <c r="B10" t="n">
-        <v>102704</v>
+        <v>102723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>128347610</v>
       </c>
       <c r="B11" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,32 +1825,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128347625</v>
+        <v>128347345</v>
       </c>
       <c r="B12" t="n">
-        <v>102704</v>
+        <v>5477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>105894</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1860,12 +1860,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1874,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703585</v>
+        <v>703485</v>
       </c>
       <c r="R12" t="n">
-        <v>6359601</v>
+        <v>6359521</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1912,11 +1922,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1928,7 +1933,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1946,32 +1951,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128347345</v>
+        <v>128347625</v>
       </c>
       <c r="B13" t="n">
-        <v>5477</v>
+        <v>102723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105894</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1981,22 +1986,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2005,10 +2000,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703485</v>
+        <v>703585</v>
       </c>
       <c r="R13" t="n">
-        <v>6359521</v>
+        <v>6359601</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2043,6 +2038,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
         <v>128347621</v>
       </c>
       <c r="B14" t="n">
-        <v>102704</v>
+        <v>102723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128347632</v>
       </c>
       <c r="B15" t="n">
-        <v>102704</v>
+        <v>102723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128347607</v>
       </c>
       <c r="B16" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128347624</v>
       </c>
       <c r="B3" t="n">
-        <v>102723</v>
+        <v>102732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>128347619</v>
       </c>
       <c r="B4" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,48 +1030,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128347617</v>
+        <v>128347623</v>
       </c>
       <c r="B5" t="n">
-        <v>109422</v>
+        <v>102732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703486</v>
+        <v>703583</v>
       </c>
       <c r="R5" t="n">
-        <v>6359605</v>
+        <v>6359604</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,6 +1117,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1114,7 +1133,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1132,62 +1151,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128347623</v>
+        <v>128347617</v>
       </c>
       <c r="B6" t="n">
-        <v>102723</v>
+        <v>109435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703583</v>
+        <v>703486</v>
       </c>
       <c r="R6" t="n">
-        <v>6359604</v>
+        <v>6359605</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,11 +1224,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
         <v>128347622</v>
       </c>
       <c r="B7" t="n">
-        <v>102723</v>
+        <v>102732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128347626</v>
       </c>
       <c r="B8" t="n">
-        <v>102723</v>
+        <v>102732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128347614</v>
       </c>
       <c r="B9" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128347627</v>
       </c>
       <c r="B10" t="n">
-        <v>102723</v>
+        <v>102732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>128347610</v>
       </c>
       <c r="B11" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128347625</v>
       </c>
       <c r="B13" t="n">
-        <v>102723</v>
+        <v>102732</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>128347621</v>
       </c>
       <c r="B14" t="n">
-        <v>102723</v>
+        <v>102732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128347632</v>
       </c>
       <c r="B15" t="n">
-        <v>102723</v>
+        <v>102732</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128347607</v>
       </c>
       <c r="B16" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -798,37 +798,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128347624</v>
+        <v>128347619</v>
       </c>
       <c r="B3" t="n">
-        <v>102732</v>
+        <v>109444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,24 +836,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703584</v>
+        <v>703525</v>
       </c>
       <c r="R3" t="n">
-        <v>6359603</v>
+        <v>6359615</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +880,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1,6 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +891,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,37 +909,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128347619</v>
+        <v>128347624</v>
       </c>
       <c r="B4" t="n">
-        <v>109435</v>
+        <v>102738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,19 +947,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703525</v>
+        <v>703584</v>
       </c>
       <c r="R4" t="n">
-        <v>6359615</v>
+        <v>6359603</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,6 +996,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1,6 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
         <v>128347623</v>
       </c>
       <c r="B5" t="n">
-        <v>102732</v>
+        <v>102738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>128347617</v>
       </c>
       <c r="B6" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>128347622</v>
       </c>
       <c r="B7" t="n">
-        <v>102732</v>
+        <v>102738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128347626</v>
       </c>
       <c r="B8" t="n">
-        <v>102732</v>
+        <v>102738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128347614</v>
       </c>
       <c r="B9" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128347627</v>
       </c>
       <c r="B10" t="n">
-        <v>102732</v>
+        <v>102738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>128347610</v>
       </c>
       <c r="B11" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,32 +1825,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128347345</v>
+        <v>128347625</v>
       </c>
       <c r="B12" t="n">
-        <v>5477</v>
+        <v>102738</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105894</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1860,22 +1860,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1884,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703485</v>
+        <v>703585</v>
       </c>
       <c r="R12" t="n">
-        <v>6359521</v>
+        <v>6359601</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1922,6 +1912,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1933,7 +1928,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1951,32 +1946,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128347625</v>
+        <v>128347345</v>
       </c>
       <c r="B13" t="n">
-        <v>102732</v>
+        <v>5477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>105894</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1986,12 +1981,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2000,10 +2005,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703585</v>
+        <v>703485</v>
       </c>
       <c r="R13" t="n">
-        <v>6359601</v>
+        <v>6359521</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2038,11 +2043,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
         <v>128347621</v>
       </c>
       <c r="B14" t="n">
-        <v>102732</v>
+        <v>102738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128347632</v>
       </c>
       <c r="B15" t="n">
-        <v>102732</v>
+        <v>102738</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128347607</v>
       </c>
       <c r="B16" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -1825,32 +1825,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128347625</v>
+        <v>128347345</v>
       </c>
       <c r="B12" t="n">
-        <v>102738</v>
+        <v>5477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>105894</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1860,12 +1860,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1874,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703585</v>
+        <v>703485</v>
       </c>
       <c r="R12" t="n">
-        <v>6359601</v>
+        <v>6359521</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1912,11 +1922,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1928,7 +1933,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1946,32 +1951,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128347345</v>
+        <v>128347625</v>
       </c>
       <c r="B13" t="n">
-        <v>5477</v>
+        <v>102738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105894</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1981,22 +1986,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2005,10 +2000,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703485</v>
+        <v>703585</v>
       </c>
       <c r="R13" t="n">
-        <v>6359521</v>
+        <v>6359601</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2043,6 +2038,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128347619</v>
       </c>
       <c r="B3" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128347624</v>
       </c>
       <c r="B4" t="n">
-        <v>102738</v>
+        <v>102739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,62 +1030,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128347623</v>
+        <v>128347617</v>
       </c>
       <c r="B5" t="n">
-        <v>102738</v>
+        <v>109449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703583</v>
+        <v>703486</v>
       </c>
       <c r="R5" t="n">
-        <v>6359604</v>
+        <v>6359605</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,11 +1103,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1133,7 +1114,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,48 +1132,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128347617</v>
+        <v>128347623</v>
       </c>
       <c r="B6" t="n">
-        <v>109444</v>
+        <v>102739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703486</v>
+        <v>703583</v>
       </c>
       <c r="R6" t="n">
-        <v>6359605</v>
+        <v>6359604</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,6 +1219,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
         <v>128347622</v>
       </c>
       <c r="B7" t="n">
-        <v>102738</v>
+        <v>102739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128347626</v>
       </c>
       <c r="B8" t="n">
-        <v>102738</v>
+        <v>102739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128347614</v>
       </c>
       <c r="B9" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128347627</v>
       </c>
       <c r="B10" t="n">
-        <v>102738</v>
+        <v>102739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>128347610</v>
       </c>
       <c r="B11" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128347625</v>
       </c>
       <c r="B13" t="n">
-        <v>102738</v>
+        <v>102739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>128347621</v>
       </c>
       <c r="B14" t="n">
-        <v>102738</v>
+        <v>102739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128347632</v>
       </c>
       <c r="B15" t="n">
-        <v>102738</v>
+        <v>102739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128347607</v>
       </c>
       <c r="B16" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128347619</v>
       </c>
       <c r="B3" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128347624</v>
       </c>
       <c r="B4" t="n">
-        <v>102739</v>
+        <v>102766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>128347617</v>
       </c>
       <c r="B5" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>128347623</v>
       </c>
       <c r="B6" t="n">
-        <v>102739</v>
+        <v>102766</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>128347622</v>
       </c>
       <c r="B7" t="n">
-        <v>102739</v>
+        <v>102766</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128347626</v>
       </c>
       <c r="B8" t="n">
-        <v>102739</v>
+        <v>102766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128347614</v>
       </c>
       <c r="B9" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128347627</v>
       </c>
       <c r="B10" t="n">
-        <v>102739</v>
+        <v>102766</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>128347610</v>
       </c>
       <c r="B11" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,32 +1825,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128347345</v>
+        <v>128347625</v>
       </c>
       <c r="B12" t="n">
-        <v>5477</v>
+        <v>102766</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105894</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1860,22 +1860,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1884,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703485</v>
+        <v>703585</v>
       </c>
       <c r="R12" t="n">
-        <v>6359521</v>
+        <v>6359601</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1922,6 +1912,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1933,7 +1928,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1951,32 +1946,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128347625</v>
+        <v>128347345</v>
       </c>
       <c r="B13" t="n">
-        <v>102739</v>
+        <v>5477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>105894</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1986,12 +1981,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2000,10 +2005,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703585</v>
+        <v>703485</v>
       </c>
       <c r="R13" t="n">
-        <v>6359601</v>
+        <v>6359521</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2038,11 +2043,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2075,7 +2075,7 @@
         <v>128347621</v>
       </c>
       <c r="B14" t="n">
-        <v>102739</v>
+        <v>102766</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128347632</v>
       </c>
       <c r="B15" t="n">
-        <v>102739</v>
+        <v>102766</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128347607</v>
       </c>
       <c r="B16" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -798,37 +798,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128347619</v>
+        <v>128347624</v>
       </c>
       <c r="B3" t="n">
-        <v>109477</v>
+        <v>102766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,19 +836,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703525</v>
+        <v>703584</v>
       </c>
       <c r="R3" t="n">
-        <v>6359615</v>
+        <v>6359603</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,6 +885,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1,6 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +901,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,37 +919,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128347624</v>
+        <v>128347619</v>
       </c>
       <c r="B4" t="n">
-        <v>102766</v>
+        <v>109477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -947,24 +957,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703584</v>
+        <v>703525</v>
       </c>
       <c r="R4" t="n">
-        <v>6359603</v>
+        <v>6359615</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,11 +1001,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1,6 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1030,48 +1030,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128347617</v>
+        <v>128347623</v>
       </c>
       <c r="B5" t="n">
-        <v>109477</v>
+        <v>102766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703486</v>
+        <v>703583</v>
       </c>
       <c r="R5" t="n">
-        <v>6359605</v>
+        <v>6359604</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,6 +1117,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1114,7 +1133,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1132,62 +1151,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128347623</v>
+        <v>128347617</v>
       </c>
       <c r="B6" t="n">
-        <v>102766</v>
+        <v>109477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703583</v>
+        <v>703486</v>
       </c>
       <c r="R6" t="n">
-        <v>6359604</v>
+        <v>6359605</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,11 +1224,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1825,32 +1825,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128347625</v>
+        <v>128347345</v>
       </c>
       <c r="B12" t="n">
-        <v>102766</v>
+        <v>5477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>105894</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1860,12 +1860,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1874,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703585</v>
+        <v>703485</v>
       </c>
       <c r="R12" t="n">
-        <v>6359601</v>
+        <v>6359521</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1912,11 +1922,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1928,7 +1933,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1946,32 +1951,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128347345</v>
+        <v>128347625</v>
       </c>
       <c r="B13" t="n">
-        <v>5477</v>
+        <v>102766</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105894</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1981,22 +1986,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2005,10 +2000,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703485</v>
+        <v>703585</v>
       </c>
       <c r="R13" t="n">
-        <v>6359521</v>
+        <v>6359601</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2043,6 +2038,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -798,37 +798,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128347624</v>
+        <v>128347619</v>
       </c>
       <c r="B3" t="n">
-        <v>102766</v>
+        <v>109490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,24 +836,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703584</v>
+        <v>703525</v>
       </c>
       <c r="R3" t="n">
-        <v>6359603</v>
+        <v>6359615</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +880,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1,6 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +891,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,37 +909,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128347619</v>
+        <v>128347624</v>
       </c>
       <c r="B4" t="n">
-        <v>109477</v>
+        <v>102779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,19 +947,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703525</v>
+        <v>703584</v>
       </c>
       <c r="R4" t="n">
-        <v>6359615</v>
+        <v>6359603</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,6 +996,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1,6 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1030,62 +1030,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128347623</v>
+        <v>128347617</v>
       </c>
       <c r="B5" t="n">
-        <v>102766</v>
+        <v>109490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703583</v>
+        <v>703486</v>
       </c>
       <c r="R5" t="n">
-        <v>6359604</v>
+        <v>6359605</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,11 +1103,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1133,7 +1114,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,48 +1132,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128347617</v>
+        <v>128347623</v>
       </c>
       <c r="B6" t="n">
-        <v>109477</v>
+        <v>102779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703486</v>
+        <v>703583</v>
       </c>
       <c r="R6" t="n">
-        <v>6359605</v>
+        <v>6359604</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,6 +1219,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
         <v>128347622</v>
       </c>
       <c r="B7" t="n">
-        <v>102766</v>
+        <v>102779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128347626</v>
       </c>
       <c r="B8" t="n">
-        <v>102766</v>
+        <v>102779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128347614</v>
       </c>
       <c r="B9" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128347627</v>
       </c>
       <c r="B10" t="n">
-        <v>102766</v>
+        <v>102779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>128347610</v>
       </c>
       <c r="B11" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128347625</v>
       </c>
       <c r="B13" t="n">
-        <v>102766</v>
+        <v>102779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>128347621</v>
       </c>
       <c r="B14" t="n">
-        <v>102766</v>
+        <v>102779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128347632</v>
       </c>
       <c r="B15" t="n">
-        <v>102766</v>
+        <v>102779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128347607</v>
       </c>
       <c r="B16" t="n">
-        <v>106944</v>
+        <v>106957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -798,37 +798,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128347619</v>
+        <v>128347624</v>
       </c>
       <c r="B3" t="n">
-        <v>109490</v>
+        <v>102783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,19 +836,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703525</v>
+        <v>703584</v>
       </c>
       <c r="R3" t="n">
-        <v>6359615</v>
+        <v>6359603</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,6 +885,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1,6 m hög. Inga frukter.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +901,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,37 +919,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128347624</v>
+        <v>128347619</v>
       </c>
       <c r="B4" t="n">
-        <v>102779</v>
+        <v>109494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -947,24 +957,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703584</v>
+        <v>703525</v>
       </c>
       <c r="R4" t="n">
-        <v>6359603</v>
+        <v>6359615</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,11 +1001,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1,6 m hög. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
         <v>128347617</v>
       </c>
       <c r="B5" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>128347623</v>
       </c>
       <c r="B6" t="n">
-        <v>102779</v>
+        <v>102783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>128347622</v>
       </c>
       <c r="B7" t="n">
-        <v>102779</v>
+        <v>102783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>128347626</v>
       </c>
       <c r="B8" t="n">
-        <v>102779</v>
+        <v>102783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>128347614</v>
       </c>
       <c r="B9" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128347627</v>
       </c>
       <c r="B10" t="n">
-        <v>102779</v>
+        <v>102783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>128347610</v>
       </c>
       <c r="B11" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128347625</v>
       </c>
       <c r="B13" t="n">
-        <v>102779</v>
+        <v>102783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>128347621</v>
       </c>
       <c r="B14" t="n">
-        <v>102779</v>
+        <v>102783</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>128347632</v>
       </c>
       <c r="B15" t="n">
-        <v>102779</v>
+        <v>102783</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>128347607</v>
       </c>
       <c r="B16" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55481790</v>
+        <v>16733633</v>
       </c>
       <c r="B2" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,25 +708,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44, Gtl</t>
+          <t>Lojsta Bjärs 1:55, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703350.1055492652</v>
+        <v>703537</v>
       </c>
       <c r="R2" t="n">
-        <v>6359855.281462963</v>
+        <v>6359661</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,51 +758,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128347624</v>
+        <v>55481495</v>
       </c>
       <c r="B3" t="n">
-        <v>102783</v>
+        <v>87322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6037533</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,27 +811,23 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703584</v>
+        <v>703340</v>
       </c>
       <c r="R3" t="n">
-        <v>6359603</v>
+        <v>6360007</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,17 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1,6 m hög. Inga frukter.</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,33 +865,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson, Dennis Nyström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128347619</v>
+        <v>16733636</v>
       </c>
       <c r="B4" t="n">
-        <v>109494</v>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,46 +895,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>3286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta Bjärs 1:55, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703525</v>
+        <v>703551</v>
       </c>
       <c r="R4" t="n">
-        <v>6359615</v>
+        <v>6359666</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,69 +974,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128347617</v>
+        <v>16733634</v>
       </c>
       <c r="B5" t="n">
-        <v>109494</v>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta Bjärs 1:55, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703486</v>
+        <v>703537</v>
       </c>
       <c r="R5" t="n">
-        <v>6359605</v>
+        <v>6359661</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,53 +1071,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128347623</v>
+        <v>55482029</v>
       </c>
       <c r="B6" t="n">
-        <v>102783</v>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6037533</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,27 +1122,23 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703583</v>
+        <v>703417</v>
       </c>
       <c r="R6" t="n">
-        <v>6359604</v>
+        <v>6359694</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,17 +1162,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 m hög. Inga frukter.</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,55 +1176,51 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128347622</v>
+        <v>55481543</v>
       </c>
       <c r="B7" t="n">
-        <v>102783</v>
+        <v>87170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6037533</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,27 +1230,23 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>703571</v>
+        <v>703359</v>
       </c>
       <c r="R7" t="n">
-        <v>6359615</v>
+        <v>6359892</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,17 +1270,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3,3 m hög. 3 stammar 1 + 1,5 + 4 cm i daimeter. Medfrukter.</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,55 +1284,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Jord- och stenhög i gles kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson, Dennis Nyström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128347626</v>
+        <v>55481648</v>
       </c>
       <c r="B8" t="n">
-        <v>102783</v>
+        <v>87146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6037533</v>
+        <v>3762</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1409,27 +1338,23 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703592</v>
+        <v>703381</v>
       </c>
       <c r="R8" t="n">
-        <v>6359590</v>
+        <v>6359775</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,17 +1378,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0,5 m hög; Under staket mot körväg.</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,68 +1392,74 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson, Dennis Nyström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128347614</v>
+        <v>55482019</v>
       </c>
       <c r="B9" t="n">
-        <v>109494</v>
+        <v>87146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>3762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703479</v>
+        <v>703377</v>
       </c>
       <c r="R9" t="n">
-        <v>6359603</v>
+        <v>6359780</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1560,17 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,33 +1500,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128347627</v>
+        <v>1796309</v>
       </c>
       <c r="B10" t="n">
-        <v>102783</v>
+        <v>87391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,51 +1530,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6037533</v>
+        <v>3767</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta hajd, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>703491</v>
+        <v>703557</v>
       </c>
       <c r="R10" t="n">
-        <v>6359527</v>
+        <v>6359658</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,17 +1593,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1,8 m hög; spenslig 1 stam 0,5 cm i diameter. Inga frukter.</t>
+          <t>2011-09-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,31 +1609,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Åke Edvinsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128347610</v>
+        <v>16733637</v>
       </c>
       <c r="B11" t="n">
-        <v>109494</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,37 +1636,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta Bjärs 1:55, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703443</v>
+        <v>703551</v>
       </c>
       <c r="R11" t="n">
-        <v>6359606</v>
+        <v>6359666</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,12 +1690,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,31 +1706,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128347345</v>
+        <v>16733635</v>
       </c>
       <c r="B12" t="n">
-        <v>5477</v>
+        <v>93233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,61 +1733,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105894</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Lojsta Bjärs 1:55, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703485</v>
+        <v>703537</v>
       </c>
       <c r="R12" t="n">
-        <v>6359521</v>
+        <v>6359661</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1914,12 +1787,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2014-09-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,55 +1801,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Länsstyrelsen i Gotlands län</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128347625</v>
+        <v>128347345</v>
       </c>
       <c r="B13" t="n">
-        <v>102783</v>
+        <v>5479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>105894</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1986,12 +1855,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2000,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703585</v>
+        <v>703485</v>
       </c>
       <c r="R13" t="n">
-        <v>6359601</v>
+        <v>6359521</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2038,11 +1917,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2054,7 +1928,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2072,62 +1946,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128347621</v>
+        <v>128782441</v>
       </c>
       <c r="B14" t="n">
-        <v>102783</v>
+        <v>104639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6037533</v>
+        <v>220164</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+          <t>Fride 1:45 (1), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703557</v>
+        <v>703602</v>
       </c>
       <c r="R14" t="n">
-        <v>6359619</v>
+        <v>6359584</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2159,11 +2019,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>6,5 m hög; Frukter ses. Stam 9 cm i diameter samt delstam 3 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2175,7 +2030,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Grustag f.d.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2193,62 +2048,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128347632</v>
+        <v>128347610</v>
       </c>
       <c r="B15" t="n">
-        <v>102783</v>
+        <v>110078</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703485</v>
+        <v>703443</v>
       </c>
       <c r="R15" t="n">
-        <v>6359521</v>
+        <v>6359606</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2280,11 +2121,6 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1,8 m hög; 1 stm 2 cm i diameter. Inga frukter.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2296,7 +2132,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2314,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128347607</v>
+        <v>128347614</v>
       </c>
       <c r="B16" t="n">
-        <v>106961</v>
+        <v>110078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,16 +2161,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2349,13 +2185,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703439</v>
+        <v>703479</v>
       </c>
       <c r="R16" t="n">
-        <v>6359632</v>
+        <v>6359603</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2387,6 +2223,11 @@
           <t>2025-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2398,7 +2239,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2413,6 +2254,2286 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128347617</v>
+      </c>
+      <c r="B17" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>703486</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6359605</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128347619</v>
+      </c>
+      <c r="B18" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>703525</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6359615</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles. Avverkat i gator.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128347607</v>
+      </c>
+      <c r="B19" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>703439</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6359632</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128782442</v>
+      </c>
+      <c r="B20" t="n">
+        <v>107516</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fride 1:45 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>703602</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6359584</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Grustag f.d.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>55481890</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>703313</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6360097</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>55481538</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>703359</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6359892</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Arne Pettersson, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>55481593</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>703385</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6359798</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Arne Pettersson, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>55481613</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>703427</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6359679</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Arne Pettersson, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>55481780</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>703327</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6360010</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>55481790</v>
+      </c>
+      <c r="B26" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>703350</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6359855</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128347621</v>
+      </c>
+      <c r="B27" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>703557</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6359619</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>6,5 m hög; Frukter ses. Stam 9 cm i diameter samt delstam 3 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128347622</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>703571</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6359615</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3,3 m hög. 3 stammar 1 + 1,5 + 4 cm i daimeter. Medfrukter.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Jord- och stenhög i gles kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128347623</v>
+      </c>
+      <c r="B29" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>703583</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6359604</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 m hög. Inga frukter.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128347624</v>
+      </c>
+      <c r="B30" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>703584</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6359603</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1,6 m hög. Inga frukter.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128347625</v>
+      </c>
+      <c r="B31" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>703585</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6359601</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>3,2 m hög; Frukter ses. Avverkad äldre stam 20 cm i diameter, nu med ca 20 stammar 1-4 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128347626</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>703592</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6359590</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>0,5 m hög; Under staket mot körväg.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128347627</v>
+      </c>
+      <c r="B33" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>703491</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6359527</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1,8 m hög; spenslig 1 stam 0,5 cm i diameter. Inga frukter.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128347632</v>
+      </c>
+      <c r="B34" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 2213-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>703485</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6359521</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1,8 m hög; 1 stm 2 cm i diameter. Inga frukter.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128782508</v>
+      </c>
+      <c r="B35" t="n">
+        <v>103305</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bjärs 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>703637</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6359608</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1,7 m hög, angripen, stam 3 cm i diameter med sidostam.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Sand-/grusås, tidigare avverkat nu rätt öppet, grustag i S-kant.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128782514</v>
+      </c>
+      <c r="B36" t="n">
+        <v>103305</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fride 1:45 (1), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>703605</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6359588</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>5 m hög delvis angripen, 5 stammar 1 + 1 +3 + 3,5 + 7 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Hästbete f.d. på sand/grus.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -3330,7 +3330,7 @@
         <v>128347621</v>
       </c>
       <c r="B27" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>128347622</v>
       </c>
       <c r="B28" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>128347623</v>
       </c>
       <c r="B29" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>128347624</v>
       </c>
       <c r="B30" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>128347625</v>
       </c>
       <c r="B31" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>128347626</v>
       </c>
       <c r="B32" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>128347627</v>
       </c>
       <c r="B33" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>128347632</v>
       </c>
       <c r="B34" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128782508</v>
       </c>
       <c r="B35" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>128782514</v>
       </c>
       <c r="B36" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 2213-2023 artfynd.xlsx
+++ b/artfynd/A 2213-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481495</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733636</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733634</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55482029</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481543</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481648</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55482019</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1796309</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733637</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16733635</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347345</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2045,6 +2110,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128782441</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347610</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347614</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,6 +2436,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347617</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347619</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2569,6 +2659,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347607</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2676,6 +2771,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128782442</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2784,6 +2884,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481890</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2892,6 +2997,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481538</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3000,6 +3110,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481593</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3108,6 +3223,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481613</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3216,6 +3336,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481780</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3324,6 +3449,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481790</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3445,6 +3575,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347621</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3566,6 +3701,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347622</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3687,6 +3827,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347623</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3808,6 +3953,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347624</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3929,6 +4079,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347625</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4050,6 +4205,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347626</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4171,6 +4331,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347627</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4292,6 +4457,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347632</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4413,6 +4583,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128782508</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4534,8 +4709,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128782514</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>